--- a/Result/profitability/1817.xlsx
+++ b/Result/profitability/1817.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.26</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.1425</v>
       </c>
       <c r="N2" t="n">
-        <v>36.815</v>
+        <v>37.17625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07125</v>
+        <v>1.12625</v>
       </c>
       <c r="N3" t="n">
-        <v>36.335</v>
+        <v>36.5425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -8177,6 +8177,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1817</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>691</v>
+      </c>
+      <c r="D62" t="n">
+        <v>428</v>
+      </c>
+      <c r="E62" t="n">
+        <v>262</v>
+      </c>
+      <c r="F62" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="G62" t="n">
+        <v>88</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>12.72%</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>64</v>
+      </c>
+      <c r="J62" t="n">
+        <v>152</v>
+      </c>
+      <c r="K62" t="n">
+        <v>127</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.11125</v>
+      </c>
+      <c r="N62" t="n">
+        <v>36.92625</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.4462809917355373</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-0.8299999999999983</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.02138073158165887</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.9230769230769229</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.690000000000005</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.04655647382920125</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
